--- a/assets/constructions/examples/ctd_mc1.xlsx
+++ b/assets/constructions/examples/ctd_mc1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO6"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,21 +634,46 @@
           <t>cpdf</t>
         </is>
       </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5408-d25</t>
+          <t>3347 7.000</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ILIX</t>
+          <t>GUHRING</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5408-ILLICO</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -656,38 +681,42 @@
           <t>PMK</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>k10</t>
+          <t>js12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="N2" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="Q2" t="n">
         <v>4</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>HB-25</t>
+          <t>HB-10</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -696,25 +725,25 @@
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>HSS-Co8</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>HSS-Co8</t>
-        </is>
-      </c>
+          <t>M42</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>DIN 1835/1_DIN 844K</t>
+          <t>DIN 844 L</t>
         </is>
       </c>
       <c r="Z2" t="n">
@@ -724,10 +753,10 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AC2" t="n">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="AD2" t="n">
         <v>30</v>
@@ -737,9 +766,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="AF2" t="n">
-        <v>12</v>
-      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
@@ -749,7 +776,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2021/Ilix-illico-ITeh.pdf</t>
+          <t>2019 - Guhring Фрезерный инструмент New Level</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -762,27 +789,38 @@
       </c>
       <c r="AO2" t="b">
         <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EM814090</t>
+          <t>3127 16.000</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>GUHRING</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EM814</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -794,31 +832,33 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="N3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>HA-10</t>
+          <t>HB-16</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -834,16 +874,20 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Micro Grain Carbide</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>TiAlN</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>DIN 6527 L</t>
+        </is>
+      </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
@@ -851,17 +895,17 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AC3" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr"/>
@@ -874,7 +918,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2017 - YG1 - General catalogue</t>
+          <t>2020 www.guhring.com</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -887,33 +931,44 @@
       </c>
       <c r="AO3" t="b">
         <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EQ762080</t>
+          <t>7450-d8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>ILIX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EQ762</t>
+          <t>7450-ILLICO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>js12</t>
+          <t>k12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -921,22 +976,20 @@
       <c r="I4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" t="n">
-        <v>8</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="N4" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="Q4" t="n">
         <v>4</v>
@@ -952,23 +1005,27 @@
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>HSS_Co8</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr"/>
+          <t>ASP-60</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>ASP-60</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>TiAlN</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>DIN 1835/1 / ILLICO NORM</t>
+        </is>
+      </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
@@ -979,7 +1036,7 @@
         <v>10</v>
       </c>
       <c r="AC4" t="n">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="AD4" t="n">
         <v>30</v>
@@ -989,7 +1046,9 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr"/>
+      <c r="AF4" t="n">
+        <v>10</v>
+      </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
@@ -999,7 +1058,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2017 - YG1 - HSS-Endmills</t>
+          <t>2021/Ilix-illico-ITeh.pdf</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1012,22 +1071,33 @@
       </c>
       <c r="AO4" t="b">
         <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3723 16.000</t>
+          <t>GAD52120</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GUHRING</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>GAD52</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1035,46 +1105,40 @@
           <t>PMK</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>h10</t>
+          <t>js12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="N5" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>HB-16</t>
+          <t>HA-12</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1090,20 +1154,16 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>HSS-PM</t>
         </is>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>FIRE</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>DIN 6527 L</t>
-        </is>
-      </c>
+          <t>X-Coating</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
@@ -1111,17 +1171,17 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AC5" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="AD5" t="n">
         <v>30</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -1134,12 +1194,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2020 www.guhring.com</t>
+          <t>2020: www.yg1.co.kr/toolselection/main/</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>HSS</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1147,33 +1207,44 @@
       </c>
       <c r="AO5" t="b">
         <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E2760120</t>
+          <t>5450-d12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>ILIX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>E2760</t>
+          <t>5450-ILLICO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>±0,12</t>
+          <t>k12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1181,22 +1252,20 @@
       <c r="I6" t="n">
         <v>12</v>
       </c>
-      <c r="J6" t="n">
-        <v>12</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="N6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Q6" t="n">
         <v>4</v>
@@ -1212,23 +1281,27 @@
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>HSS-Co8</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr"/>
+          <t>ASP-60</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>ASP-60</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>DIN 1835/1 / DIN 844 K</t>
+        </is>
+      </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
@@ -1239,7 +1312,7 @@
         <v>12</v>
       </c>
       <c r="AC6" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AD6" t="n">
         <v>30</v>
@@ -1249,7 +1322,9 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>10</v>
+      </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
@@ -1259,7 +1334,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2020: www.yg1.co.kr/toolselection/main/</t>
+          <t>2021/Ilix-illico-ITeh.pdf</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1272,6 +1347,17 @@
       </c>
       <c r="AO6" t="b">
         <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
       </c>
     </row>
   </sheetData>
